--- a/e2e-screenshots/model-picker-bucket-filter/bucket-fixture-sales.xlsx
+++ b/e2e-screenshots/model-picker-bucket-filter/bucket-fixture-sales.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -493,9 +493,56 @@
         <v/>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2026-07-24</v>
+      </c>
+      <c r="B3" t="str">
+        <v>ORPHAN-BUCKET-TEST-2</v>
+      </c>
+      <c r="C3" t="str">
+        <v>SKU-Y</v>
+      </c>
+      <c r="D3" t="str">
+        <v>350000000088888</v>
+      </c>
+      <c r="E3" t="str">
+        <v>TESTSUP</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>90</v>
+      </c>
+      <c r="H3">
+        <v>140</v>
+      </c>
+      <c r="I3" t="str">
+        <v/>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3">
+        <v>6.3</v>
+      </c>
+      <c r="M3" t="str">
+        <v/>
+      </c>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O3"/>
   </ignoredErrors>
 </worksheet>
 </file>